--- a/UnityBasic2/Assets/Data/Data.xlsx
+++ b/UnityBasic2/Assets/Data/Data.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\Project\ProjectBS\ProjectBS\Assets\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\H\Documents\GitHub\UnityBasic2\UnityBasic2\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D5624E0-82EA-45F1-8ED0-E4766F84D709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E01257F-78BA-4DA1-94F2-F461A080A7E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12105" yWindow="1740" windowWidth="16530" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Test" sheetId="1" r:id="rId1"/>
+    <sheet name="Test" sheetId="3" r:id="rId1"/>
+    <sheet name="Dialogue" sheetId="1" r:id="rId2"/>
+    <sheet name="Character" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,9 +27,80 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
-  <si>
-    <t>Name_S</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="21">
+  <si>
+    <t>ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Character</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Position</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Title</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Image</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>벤리아나</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>02_default</t>
+  </si>
+  <si>
+    <t>BG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Description</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>벤리아나_기본_표정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>03_surprise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>벤리아나_놀란_표정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>04_smile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>벤리아나_웃는_표정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전 바보가 된 레이나도 좋다고 생각합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BG_02</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -35,7 +108,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>bbno</t>
+    <t>그렇습니까.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -59,12 +132,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -79,8 +158,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -360,24 +448,175 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4B9FC25-C335-4356-89E0-6CC36FB966F0}">
+  <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="17.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="76.25" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>10102</v>
+      </c>
+      <c r="C2" s="1">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>10103</v>
+      </c>
+      <c r="C3" s="1">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B43F9829-2E15-44CB-B4E0-48C443EFDAC1}">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="23.375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="29.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="55.5" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>10101</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>10102</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>10103</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
